--- a/www/download/COUNTRY.IDN.rpA1.xlsx
+++ b/www/download/COUNTRY.IDN.rpA1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Indonésia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>2272.72725159669</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>2325.58149802397</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>2777.77771550454</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>10000.0002563893</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>7692.30773458784</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>8333.33350296015</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>10000.0001758223</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>9090.90898453412</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>8333.33356401223</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>9090.90905747659</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>10000.0002875486</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>9090.90904036155</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>9090.90895342725</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>9630.849462629</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>10324.520558605</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>87.271</t>
+          <t>-0.0427990368012198</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>88.91</t>
+          <t>0.168874115198684</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>90.204</t>
+          <t>0.470935021236863</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>90.827</t>
+          <t>0.799477232600831</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>92.114</t>
+          <t>1.20718079792629</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>93.321</t>
+          <t>0.470553051655174</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>93.437</t>
+          <t>0.422143538241949</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>93.655</t>
+          <t>0.420768814376112</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>94.323</t>
+          <t>0.220509406209054</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>94.695</t>
+          <t>0.346577494032472</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>95.464</t>
+          <t>-0.0450099978995199</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>97.88</t>
+          <t>-0.078666952462494</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>103.349</t>
+          <t>-0.206514695355838</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>105.753</t>
+          <t>-0.173582162691058</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>108.203</t>
+          <t>-0.203927845601936</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>29.411</t>
+          <t>0.696551718763108</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30.648</t>
+          <t>0.882045101565677</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.685</t>
+          <t>1.04714415569733</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.287</t>
+          <t>1.33148699103309</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>33.271</t>
+          <t>1.46905579750387</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>32.856</t>
+          <t>1.30480620520425</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35.315</t>
+          <t>1.1517166977863</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35.183</t>
+          <t>1.0019166615587</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>33.625</t>
+          <t>0.894868539652488</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>34.679</t>
+          <t>0.788760636804657</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>36.447</t>
+          <t>0.818288402108243</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>38.129</t>
+          <t>0.906203824191582</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>40.067</t>
+          <t>0.834157007503591</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>40.926</t>
+          <t>0.883555194072249</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>42.189</t>
+          <t>0.881277904581257</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>126800.04</t>
+          <t>1.49081311942167</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>130791.792</t>
+          <t>1.44120955553774</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>130793.751</t>
+          <t>1.87743887670766</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>135652.383</t>
+          <t>1.83882266572251</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>151359.325</t>
+          <t>1.78545238008871</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>150969.555</t>
+          <t>1.73267091311734</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>152843.242</t>
+          <t>1.82680210067027</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>160887.359</t>
+          <t>1.87581712332645</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>164503.981</t>
+          <t>1.62195341816081</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>171431.406</t>
+          <t>1.83017133819139</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>147126.681</t>
+          <t>1.70593185002197</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>138944.74</t>
+          <t>1.54434649810691</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>142588.35</t>
+          <t>1.45599571605418</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>146166.663</t>
+          <t>1.4998300438273</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>149772.086</t>
+          <t>1.38688041932926</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>50845.365</t>
+          <t>140408758499.751</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53343.046</t>
+          <t>145739497609.845</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>55663.7</t>
+          <t>141603090181.534</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>55335.436</t>
+          <t>132851521427.75</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>63289.03</t>
+          <t>151034009095.324</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>61997.762</t>
+          <t>159377755140.334</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>64581.67</t>
+          <t>163014548636.888</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>67000.017</t>
+          <t>173597844307.903</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>65303.248</t>
+          <t>179749532800.466</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>69112.816</t>
+          <t>177958757047.086</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>60280.812</t>
+          <t>158021336582.946</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>57540.415</t>
+          <t>152566466200.504</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>57444.212</t>
+          <t>158754976380.612</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>58630.515</t>
+          <t>162194186513.12</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>60602.234</t>
+          <t>170799794422.201</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>25158044059.7051</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>25499059652.6596</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>22957016398.6178</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>21833500353.8602</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12.81</t>
+          <t>24213578764.8576</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>25959248108.8638</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>27084571330.7367</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16.08</t>
+          <t>28483406774.114</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>30604834399.8748</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>15.61</t>
+          <t>31255712790.7079</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>29672697619.8583</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>29671827111.28</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>31689841813.4956</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>31472947492.5357</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.83</t>
+          <t>33742451323.6668</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>11138914.7533463</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>10041842.1259682</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>9708413.49373121</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.23</t>
+          <t>24026996.3297513</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>16295421.5155601</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>30.71</t>
+          <t>14388030.9473635</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>14907252.2937106</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>13197368.5525513</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>11280770.6926913</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>33.79</t>
+          <t>11189442.7592244</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>9403016.04632278</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>6675734.06412355</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>5666980.47176559</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>4930099.01950721</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>4891803.19493737</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>51.33</t>
+          <t>676877.336184275</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.33</t>
+          <t>685747.455691954</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>50.29</t>
+          <t>657812.564462933</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>672998.028602778</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>50.89</t>
+          <t>761051.227051583</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>46.48</t>
+          <t>832491.430931072</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>819363.69211957</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>876843.330526353</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>968395.218489516</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>1075765.52224927</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>1041899.53093869</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>1019228.10497021</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>1184148.30838317</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>1321434.40190386</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>1252769.2227402</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>1092999.94026476</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>1142986.02570362</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>1103416.16618006</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7.04</t>
+          <t>1029612.6045958</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>1219047.65614973</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>1313035.8439106</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>1307687.28532044</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>1423602.25921686</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>1587926.14979748</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8.66</t>
+          <t>1732606.97530745</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>1647685.43300144</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>1667348.66628731</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>1962587.10823928</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>2220006.90914426</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>2180736.4283481</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>1.02103807950437</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>1.09196128202433</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>1.42469224042939</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>1.53442807762236</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>25.47</t>
+          <t>1.61378257620854</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>1.38827263055928</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>1.38444497873505</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>1.35224731319554</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>1.13375598209048</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>1.21120587794553</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>1.03152449129189</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>0.939227210426181</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.812701115547288</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.862886045005517</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.796023460493619</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>66.08</t>
+          <t>48825.329334992</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>64.14</t>
+          <t>53890.5594980207</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>63.89</t>
+          <t>51037.0041872361</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.93</t>
+          <t>26742.7088390645</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>61.66</t>
+          <t>31284.4814312497</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>33934.4750191497</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>33025.3248152127</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>58.49</t>
+          <t>37162.4702735546</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>56.77</t>
+          <t>41722.9342117947</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>49851.9702950525</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>55.95</t>
+          <t>51938.7931268496</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>55.18</t>
+          <t>67691.0060264783</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>80102.8851228427</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>97543.8631333117</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>97844.1351524629</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2272.72725159669</t>
+          <t>855.393830091407</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2325.58149802397</t>
+          <t>831.988633175514</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2777.77771550454</t>
+          <t>702.36188803517</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10000.0002563893</t>
+          <t>697.851049106005</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7692.30773458784</t>
+          <t>727.772158273081</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8333.33350296015</t>
+          <t>790.092740173204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10000.0001758223</t>
+          <t>766.937803710358</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9090.90898453412</t>
+          <t>809.576986520478</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8333.33356401223</t>
+          <t>910.175268830872</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>9090.90905747659</t>
+          <t>901.279876546361</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10000.0002875486</t>
+          <t>814.123546478489</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>9090.90904036155</t>
+          <t>778.191522679898</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>9090.90895342725</t>
+          <t>790.923848661642</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>9630.849462629</t>
+          <t>769.019401700109</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>10324.520558605</t>
+          <t>799.793256749357</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-5538523074.84846</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>-3749121206.73079</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>-3313928105.39499</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>-14131146040.2905</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>-10047082887.0402</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>-13178576240.744</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>-12562609475.9368</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>-9072596083.84887</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-8578801602.40393</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>-9727656254.70406</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>-8669702403.58386</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>-3115494038.5213</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>-2692315906.91664</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-3916655795.75892</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-1434228074.63474</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>-5382467873.32474</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>-3482312439.66752</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>-2932106607.5612</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>-13900902119.6273</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>-9756145062.15065</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>-12688232963.4493</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>-12166986289.979</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>-8778049366.19231</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>-8448502215.66845</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>-9669036355.56269</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-8107910712.45442</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>-2495987236.81858</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>-2057328104.45066</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>-3448184835.07712</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>-1060578428.91854</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>-156055201.523718</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>-266808767.063273</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>-381821497.833787</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>-230243920.663256</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>-290937824.889525</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>-490343277.294683</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>-395623185.957725</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.508</t>
+          <t>-294546717.656556</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>-130299386.735474</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>-58619899.1413764</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>-561791691.129436</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.965</t>
+          <t>-619506801.702717</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>-634987802.465976</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.304</t>
+          <t>-468470960.681802</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>-373649645.716207</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>1728.78350358782</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>1740.48800768752</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1703.01141989221</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>1768.65329285248</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>1902.23818674387</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>1886.95686695924</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>1828.72099505925</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>1904.32529136774</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>1942.09192461869</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>1992.91536069333</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.541</t>
+          <t>1653.91192360846</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1509.09017570384</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1433.70854278191</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.011</t>
+          <t>1432.59551176563</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.075</t>
+          <t>1436.44745266644</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>1452.94260373102</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>1471.0541085881</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>1449.98387617908</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>1493.52915423491</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>1643.16752143074</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>1617.74556456219</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>1635.7885255496</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>1717.87340451198</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>1744.05781266345</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>1810.34425139452</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>1541.1768690321</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>1419.54506565479</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>1379.67304594222</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>1382.14849067478</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>1384.1795844665</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>54138.457699988</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>61053.5719199881</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>64405.7864399881</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>79.95</t>
+          <t>49432.225459988</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>120.72</t>
+          <t>51848.517879988</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>65346.247149988</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>64404.5237059486</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>65533.6910050178</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>22.05</t>
+          <t>73677.0230267382</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>81394.0512065612</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>93886.8189276342</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>112559.643523315</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-20.65</t>
+          <t>125466.079246621</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-17.36</t>
+          <t>150603.286883368</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-20.39</t>
+          <t>130588.269769243</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>12759698952.7113</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>12439175449.0905</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>104.71</t>
+          <t>12689107291.65</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>133.15</t>
+          <t>21594952521.8319</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>146.91</t>
+          <t>18600649214.8505</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>130.48</t>
+          <t>24549519977.3371</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>115.17</t>
+          <t>24932213469.7083</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>100.19</t>
+          <t>22956484653.5669</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>23149079145.1712</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>78.88</t>
+          <t>24696816775.3253</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>81.83</t>
+          <t>22106144225.6564</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>18838442033.1904</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>83.42</t>
+          <t>19232739742.2458</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>20113757119.8133</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>16942471469.6108</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>149.08</t>
+          <t>52847.5461274449</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>144.12</t>
+          <t>58053.2478633127</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>187.74</t>
+          <t>60132.0333709756</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>183.88</t>
+          <t>36952.9266551684</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>178.55</t>
+          <t>37259.6350323168</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>173.27</t>
+          <t>47322.1241286864</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>182.68</t>
+          <t>48730.331099414</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>187.58</t>
+          <t>50158.9369691569</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>52966.5424989152</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>183.02</t>
+          <t>65882.0796669503</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>170.59</t>
+          <t>78243.8457267915</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>154.43</t>
+          <t>88144.2207202457</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>145.6</t>
+          <t>102583.447461945</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>149.98</t>
+          <t>137567.517918979</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>138.69</t>
+          <t>109126.096597017</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>126800.04</t>
+          <t>7021836270.69976</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>130791.792</t>
+          <t>8245326127.56326</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>130793.751</t>
+          <t>8790312966.06015</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>135652.383</t>
+          <t>5666106857.60871</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>151359.325</t>
+          <t>6404566419.64508</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>150969.555</t>
+          <t>8695199666.06059</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>152843.242</t>
+          <t>9922802166.93361</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>160887.359</t>
+          <t>11510562598.6044</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>164503.981</t>
+          <t>11554171702.552</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>171431.406</t>
+          <t>12897612921.7569</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>147126.681</t>
+          <t>11500058662.1185</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>138944.74</t>
+          <t>12966366726.6812</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>142588.35</t>
+          <t>14262415945.8352</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>146166.663</t>
+          <t>15048465202.8143</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>149772.086</t>
+          <t>13428912094.2655</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>50845.365</t>
+          <t>1290.91157254311</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>53343.046</t>
+          <t>3000.32405667541</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>55663.7</t>
+          <t>4273.75306901255</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>55335.436</t>
+          <t>12479.2988048195</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>63289.03</t>
+          <t>14588.8828476712</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>61997.762</t>
+          <t>18024.1230213016</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>64581.67</t>
+          <t>15674.1926065346</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>67000.017</t>
+          <t>15374.7540358609</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>65303.248</t>
+          <t>20710.480527823</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>69112.816</t>
+          <t>15511.9715396109</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>60280.812</t>
+          <t>15642.9732008427</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>57540.415</t>
+          <t>24415.4228030691</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>57444.212</t>
+          <t>22882.6317846762</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>58630.515</t>
+          <t>13035.7689643891</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>60602.234</t>
+          <t>21462.173172226</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>140408.758</t>
+          <t>5737862682.01153</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>145739.498</t>
+          <t>4193849321.52721</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>141603.09</t>
+          <t>3898794325.58985</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>132851.521</t>
+          <t>15928845664.2232</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>151034.009</t>
+          <t>12196082795.2054</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>159377.755</t>
+          <t>15854320311.2765</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>163014.549</t>
+          <t>15009411302.7747</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>173597.844</t>
+          <t>11445922054.9625</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>179749.533</t>
+          <t>11594907442.6192</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>177958.757</t>
+          <t>11799203853.5684</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>158021.337</t>
+          <t>10606085563.5379</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>152566.466</t>
+          <t>5872075306.5092</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>158754.976</t>
+          <t>4970323796.41052</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>162194.187</t>
+          <t>5065291916.99898</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>170799.794</t>
+          <t>3513559375.34532</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>155976.45275</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>183352.474</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.103</t>
+          <t>185099.45575</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>73327.91787</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>107424.47103</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.313</t>
+          <t>116205.18664</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.308</t>
+          <t>112488.62669</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.424</t>
+          <t>133427.4942</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>154571.72139</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>161614.73025</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>179589.30615</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>240124.54312</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.963</t>
+          <t>285485.93308</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>346916.28902</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.181</t>
+          <t>368723.7386</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>86952.893</t>
+          <t>0.12431164765859</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>87438.068</t>
+          <t>0.136551161153083</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>84418.096</t>
+          <t>0.157347732027776</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>86837.332</t>
+          <t>0.0842016748048549</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>94290.504</t>
+          <t>0.0997218622344326</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>101048.738</t>
+          <t>0.112682096450463</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>102140.782</t>
+          <t>0.123726130846616</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>106924.607</t>
+          <t>0.136128442734515</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>109620.078</t>
+          <t>0.127062010310847</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>110493.55</t>
+          <t>0.118798736156979</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>99923.416</t>
+          <t>0.134642694138362</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>93261.855</t>
+          <t>0.135824903526462</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>95786.544</t>
+          <t>0.136980894913364</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>96544.284</t>
+          <t>0.139369998316011</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>98119.481</t>
+          <t>0.143597765689627</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>74685.9170336728</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>85768.7808002433</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>85466.0101454388</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>32372.7188251886</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>49043.8056157691</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>52170.1354876091</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>51127.5688411985</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>62032.9060123352</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>74664.3211104431</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>78881.0507419105</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.042</t>
+          <t>86065.0585550075</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>114791.24778633</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.184</t>
+          <t>135475.775248298</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>159754.246728171</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>170476.095240995</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>25158.044</t>
+          <t>122218.850226017</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>25499.06</t>
+          <t>139139.692155326</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22957.016</t>
+          <t>137534.487450055</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>21833.5</t>
+          <t>55881.1880880761</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>24213.579</t>
+          <t>84495.8385922481</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>25959.248</t>
+          <t>87083.2944607133</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>27084.571</t>
+          <t>82155.3075983676</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>28483.407</t>
+          <t>98587.9465131236</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>30604.834</t>
+          <t>121341.893929067</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>31255.713</t>
+          <t>123970.13623611</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>29672.698</t>
+          <t>129692.577799816</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>29671.827</t>
+          <t>168552.94623058</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>31689.842</t>
+          <t>201540.137830582</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>31472.947</t>
+          <t>234885.642430745</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>33742.451</t>
+          <t>249384.961977804</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>102.1</t>
+          <t>565338.501762948</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>109.2</t>
+          <t>621007.901438404</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>142.47</t>
+          <t>571610.639337541</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>328153.034567267</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>161.38</t>
+          <t>473266.443877202</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>138.83</t>
+          <t>471412.635755221</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>138.44</t>
+          <t>438062.393574817</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>135.22</t>
+          <t>508414.653859651</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>113.38</t>
+          <t>618407.651877284</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>662623.014564901</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>103.15</t>
+          <t>711488.528704662</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>93.92</t>
+          <t>964991.64240088</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>81.27</t>
+          <t>1116617.31158432</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>86.29</t>
+          <t>1303614.24898626</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>1368202.98621071</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>11.139</t>
+          <t>122218.850226017</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10.042</t>
+          <t>130160.721878188</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.708</t>
+          <t>134797.941171521</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>24.027</t>
+          <t>117295.902143358</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>16.295</t>
+          <t>116945.930469545</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14.388</t>
+          <t>122230.707891744</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>14.907</t>
+          <t>123083.155533244</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>13.197</t>
+          <t>125914.01088163</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>11.281</t>
+          <t>137572.571452366</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>11.189</t>
+          <t>142971.135448487</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9.403</t>
+          <t>147476.548897103</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6.676</t>
+          <t>153953.62165738</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>5.667</t>
+          <t>166872.985835487</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>177498.486813025</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4.892</t>
+          <t>186280.486882258</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>74685.9170336728</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>79973.398473357</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>83068.6002247067</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>68629.6395226062</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>69223.4878698862</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>73506.0442984722</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>76886.2697030478</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>80142.9843630554</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>84835.5291652548</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>90395.4653749394</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>96477.4935537934</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>102550.169774946</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>109567.402333997</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>116937.317715218</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>122877.990778738</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>119103.489973983</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>138689.909524674</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>140978.641889945</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>54373.7439419239</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>78479.4925477519</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>87054.2391092866</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>87225.0898416324</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>106372.165366876</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>120299.053650933</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>128570.74697389</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>147735.525480184</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>198760.90275942</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>233058.123739418</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>279228.578819255</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>294315.026982196</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>50845365050.5126</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>53343045521.3928</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>55663699525.1387</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>55335436329.601</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>63289030283.2379</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>61997761768.2972</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>64581670110.7665</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>67000017055.0654</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>65303248481.6216</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>69112815842.1906</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>60280811937.4406</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>57540414517.2555</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>57444211606.8405</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>58630514679.0361</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>60602234191.8695</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>126800040199.903</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>130791791531.132</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>130793750834.673</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>135652382970.267</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>151359324800.349</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>150969554560.976</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>152843242257.524</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>160887359160.359</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>164503980589.901</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>171431405963.774</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>147126680531.104</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>138944740444.118</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>142588349836.274</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>146166663137.177</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>149772086036.291</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>86952892611.5324</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>87438067861.1118</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>84418096039.5599</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>86837332428.3994</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>94290504041.1305</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>101048738349.897</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>102140782387.125</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>106924606918.56</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>109620077805.19</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>110493549859.81</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>99923415699.6597</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>93261855406.52</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>95786544168.8166</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>96544284148.1362</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>98119480612.5981</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>87271197</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>88910252.0210243</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>90203589.8353118</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>90826739.1939587</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>92114360.1162204</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>93320951</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>93437042.6679519</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>93654956.6096022</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>94322550.2018638</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>94695473.4336958</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>95463852</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>97879767.1210441</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>103349377.053964</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>105753227.039894</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>108202785.041088</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>29411065.6105816</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>30648326.955304</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>32685452.8836112</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>31286762.9587007</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>33270823.1410138</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>32855950.6864638</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>35315212.263243</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>35183073.6895503</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>33625209.8336917</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>34679252.9202777</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>36447413.5998256</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>38129208.872769</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>40066868.4692204</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>40926077.3173692</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>42188967.0098096</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>126800040199.903</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>130791791531.132</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>130793750834.673</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>135652382970.267</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>151359324800.349</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>150969554560.976</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>152843242257.524</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>160887359160.359</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>164503980589.901</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>171431405963.774</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>147126680531.104</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>138944740444.118</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>142588349836.274</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>146166663137.177</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>149772086036.291</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>50845365050.5126</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>53343045521.3928</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>55663699525.1387</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>55335436329.601</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>63289030283.2379</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>61997761768.2972</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>64581670110.7665</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>67000017055.0654</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>65303248481.6216</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>69112815842.1906</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>60280811937.4406</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>57540414517.2555</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>57444211606.8405</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>58630514679.0361</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>60602234191.8695</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.133862708237547</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.133862708237547</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.128514223825904</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.135152816633772</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.128149526003451</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.171006830839444</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.165549247462437</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.160804156557938</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.158431611105688</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.156059065653439</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.207353637961907</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.233000924116142</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.228273588657747</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.228273588657747</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.228273588657747</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.295696859929278</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.295696859929278</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.3114356161181</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.312318424954401</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.305843787252101</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.307091871869717</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.306444040432225</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.322153545857454</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.330008298570068</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.337863051282682</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.299021406845584</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.279600584627035</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.295540888760317</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.295540888760317</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.295540888760317</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.513297574690318</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.513297574690318</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.502907302913139</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.49538590126897</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.508863829601591</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.464758440147982</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.47086385496248</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.459899440441751</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.454417233181387</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.448935025921022</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.436482098049651</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.430255634113966</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.419042665439079</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.419042665439079</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.419042665439079</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0566899406941814</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0643997535174709</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0620781901604071</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0703749051182925</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0715979891524097</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0829424277174645</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.082612516283083</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0841527025971551</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.0782006947582791</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0866247519904517</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0927822374252588</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.0989397228600659</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.0927684627595972</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.0927684627595972</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.0927684627595972</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.225387955959682</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.237009789150174</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.241919450531589</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.25317786226604</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.254701099488972</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.275240379535049</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.268840320941189</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.273826824067002</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.29698568126144</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.288957028372602</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.290555367595629</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.292153706818657</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.281321561177494</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.281321561177494</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.281321561177494</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.66077924620328</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.641447600189498</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.638859502165147</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.619304375472811</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.616558054215761</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.58467433560463</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.591404305632871</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.584877616192986</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.567670766837423</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.567275362494089</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.559519537836255</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.55176371317842</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.568767118920052</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.568767118920052</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.568767118920052</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>461613.99355</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>546448.71254</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>559879.86354</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>212809.83347</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>319134.84753</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>341267.60961</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>334647.75648</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>406241.6321</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>477806.10011</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>498135.18658</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>540977.33985</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>720141.36381</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>849793.95493</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1010597.25217</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1074781.69159</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>241322.3402</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>277829.60168</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>278513.12934</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>110254.93203</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>162975.33114</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>174137.53357</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>169380.39744</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>204960.11188</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>241640.94758</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>252540.88321</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>277428.10328</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>367313.84899</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>434598.26157</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>514114.22125</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>543699.98896</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1284860221.97693</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1355540267.92</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1435586957.90658</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1453125635.01024</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1449814825.64989</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1463501173.80377</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1480376710.52065</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1496236566.85874</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1512417854.28128</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1545191911.31936</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1590299610.3592</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1635814017.64172</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1691586342.68242</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>1761628779.98288</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1832545832.63627</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
